--- a/Excels/#Airplane.xlsx
+++ b/Excels/#Airplane.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -105,6 +105,26 @@
   </si>
   <si>
     <t>Aircraft01</t>
+  </si>
+  <si>
+    <t>player_speed_rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ammo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestEmitter_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -453,14 +473,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
     <col min="4" max="4" width="19.90625" customWidth="1"/>
+    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.90625" customWidth="1"/>
+    <col min="11" max="11" width="18.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -491,8 +514,14 @@
       <c r="J1" t="s">
         <v>13</v>
       </c>
+      <c r="K1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -523,8 +552,14 @@
       <c r="J2" t="s">
         <v>16</v>
       </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -538,7 +573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -559,6 +594,12 @@
       </c>
       <c r="J4">
         <v>0.6</v>
+      </c>
+      <c r="K4">
+        <v>4</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/#Airplane.xlsx
+++ b/Excels/#Airplane.xlsx
@@ -123,7 +123,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TestEmitter_1</t>
+    <t>emeny_ammo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/Excels/#Airplane.xlsx
+++ b/Excels/#Airplane.xlsx
@@ -123,7 +123,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>emeny_ammo</t>
+    <t>enemy_ammo</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -481,6 +481,7 @@
     <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12.90625" customWidth="1"/>
     <col min="11" max="11" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">

--- a/Excels/#Airplane.xlsx
+++ b/Excels/#Airplane.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -124,6 +124,17 @@
   </si>
   <si>
     <t>enemy_ammo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dead_events</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>event_enemy_death_1</t>
+  </si>
+  <si>
+    <t>array,string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -473,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.6328125" customWidth="1"/>
@@ -484,7 +495,7 @@
     <col min="12" max="12" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -521,8 +532,11 @@
       <c r="L1" t="s">
         <v>25</v>
       </c>
+      <c r="M1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -559,8 +573,11 @@
       <c r="L2" t="s">
         <v>26</v>
       </c>
+      <c r="M2" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -574,7 +591,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>19</v>
       </c>
@@ -601,6 +618,9 @@
       </c>
       <c r="L4" t="s">
         <v>27</v>
+      </c>
+      <c r="M4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Excels/#Airplane.xlsx
+++ b/Excels/#Airplane.xlsx
@@ -127,14 +127,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dead_events</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>event_enemy_death_1</t>
   </si>
   <si>
     <t>array,string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dead_triggers</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -533,7 +533,7 @@
         <v>25</v>
       </c>
       <c r="M1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -574,7 +574,7 @@
         <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -620,7 +620,7 @@
         <v>27</v>
       </c>
       <c r="M4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
